--- a/20260805_従業員管理_使い方.xlsx
+++ b/20260805_従業員管理_使い方.xlsx
@@ -470,6 +470,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -514,7 +515,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>01_受入条件表.xlsx</t>
+          <t>01_確認表.xlsx</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -562,6 +563,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -654,6 +656,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -726,6 +729,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr"/>
     </row>
+    <row r="23"/>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -971,6 +975,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
@@ -1030,6 +1035,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr"/>
     </row>
+    <row r="45"/>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
@@ -1122,6 +1128,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
@@ -1207,6 +1214,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr"/>
     </row>
+    <row r="60"/>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
@@ -1275,6 +1283,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr"/>
     </row>
+    <row r="67"/>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>

--- a/20260805_従業員管理_使い方.xlsx
+++ b/20260805_従業員管理_使い方.xlsx
@@ -470,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -515,7 +514,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>01_確認表.xlsx</t>
+          <t>01_受入条件表.xlsx</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -563,7 +562,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -656,7 +654,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -729,7 +726,6 @@
       </c>
       <c r="C22" s="4" t="inlineStr"/>
     </row>
-    <row r="23"/>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -975,7 +971,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
@@ -1035,7 +1030,6 @@
       </c>
       <c r="C44" s="4" t="inlineStr"/>
     </row>
-    <row r="45"/>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
@@ -1128,7 +1122,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
@@ -1214,7 +1207,6 @@
       </c>
       <c r="C59" s="4" t="inlineStr"/>
     </row>
-    <row r="60"/>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
@@ -1283,7 +1275,6 @@
       </c>
       <c r="C66" s="4" t="inlineStr"/>
     </row>
-    <row r="67"/>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
